--- a/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_fewshot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_fewshot.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -20536,7 +20536,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21097,7 +21097,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21352,7 +21352,7 @@
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21743,7 +21743,7 @@
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -21760,7 +21760,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -22627,7 +22627,7 @@
       </c>
       <c r="C1306" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22644,7 +22644,7 @@
       </c>
       <c r="C1307" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="C1312" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -23035,7 +23035,7 @@
       </c>
       <c r="C1330" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -23477,7 +23477,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23766,7 +23766,7 @@
       </c>
       <c r="C1373" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8043165467625899</v>
+        <v>0.7971223021582734</v>
       </c>
     </row>
     <row r="3">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7368010859506249</v>
+        <v>0.7210291752720959</v>
       </c>
     </row>
     <row r="4">
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8005972679983053</v>
+        <v>0.7918511607165528</v>
       </c>
     </row>
     <row r="5">
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7947980747322851</v>
+        <v>0.7931091447076037</v>
       </c>
     </row>
     <row r="6">
@@ -24149,7 +24149,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7235819173276701</v>
+        <v>0.7087299195874857</v>
       </c>
     </row>
     <row r="7">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.6753345049997</v>
+        <v>769.212038261001</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2069606723057552</v>
+        <v>0.5533899555834539</v>
       </c>
     </row>
   </sheetData>
